--- a/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M06/second/CF_M06_req_eval.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M06/second/CF_M06_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.377</v>
       </c>
       <c r="D13" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9359</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>The system shall allow the partner to create a new location for a client.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -772,10 +776,6 @@
           <t>Partners to create a new location for a client.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,10 +806,6 @@
           <t>The system shall allow the partner to consult the current status of their clients' players.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -823,10 +819,6 @@
           <t>Partners to consult the current status of the different players of their clients.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -857,14 +849,11 @@
           <t>The system shall allow the user to filter and sort the client list.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -878,14 +867,11 @@
           <t>The user can filter the list by different criteria and sort the list.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>CF_M06_R01</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -916,14 +902,11 @@
           <t>The system shall use the Google Maps API to facilitate address searching when creating a new location.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>R_06</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -937,14 +920,11 @@
           <t>The Google Maps API is used to facilitate address search, making it easier to fill out form fields.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>CF_M06_R09</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -975,10 +955,6 @@
           <t>The system shall allow the partner to consult the list of their clients.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>FR</t>
@@ -992,10 +968,6 @@
           <t>Partners to consult the list of their clients.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1026,10 +998,6 @@
           <t>The system shall allow the partner to perform real-time actions on a player.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1043,10 +1011,6 @@
           <t>Partners to perform different actions on a player in real time.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1077,10 +1041,6 @@
           <t>The system shall allow the partner to change their password.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1094,10 +1054,6 @@
           <t>Partners to change their password.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1128,14 +1084,11 @@
           <t>The system shall provide buttons to restart, shut down, force synchronization, and restart playback for a player.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1149,14 +1102,11 @@
           <t>On the player screen, buttons are displayed for different actions: restart players, turn off, force synchronization, and restart playback.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M06_R17</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1187,10 +1137,6 @@
           <t>The system shall allow the partner to consult the list of locations for a selected client.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1204,14 +1150,11 @@
           <t>The user can select a client and consult the list of locations.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M06_R01</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1242,10 +1185,6 @@
           <t>The system shall allow the partner to customize push notifications.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1259,10 +1198,6 @@
           <t>Partners to customize push notifications.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1293,10 +1228,6 @@
           <t>The system shall allow the partner to receive push notifications.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1310,10 +1241,6 @@
           <t>Partners to receive push notifications.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1344,14 +1271,11 @@
           <t>The system shall display a list of locations with their respective players.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>R_04</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1365,14 +1289,11 @@
           <t>A list of locations with their respective players is displayed.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>CF_M06_R05</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1403,14 +1324,11 @@
           <t>The system shall display a list of clients with basic data.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1424,14 +1342,11 @@
           <t>A list of clients with basic data is displayed.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M06_R01</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1462,10 +1377,6 @@
           <t>The system shall allow the partner to initiate the registration process of a player by scanning a QR code.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1479,10 +1390,6 @@
           <t>Partners to initiate the player registration process by scanning the QR code displayed on the screen.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1513,14 +1420,11 @@
           <t>The user shall be able to set notification types at three levels: general, per client, and per player.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>R_14</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1534,14 +1438,11 @@
           <t>The user can set the types of notifications they want to receive at 3 levels (general, per client, and per player).</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>CF_M06_R34</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1572,14 +1473,11 @@
           <t>If the QR code is valid, the system shall navigate to the screens for selecting the client and location.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_08</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1593,14 +1491,11 @@
           <t>If the QR code is scanned correctly and is valid, the system navigates to the subsequent screens to select the client and location.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M06_R12</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1636,9 +1531,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1662,8 +1554,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1699,9 +1589,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1725,8 +1612,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1757,14 +1642,11 @@
           <t>The password must have a minimum of 8 characters, at least one uppercase letter, one number, and one special character.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_16</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1778,14 +1660,11 @@
           <t>The password must have a minimum of 8 characters, at least one uppercase letter, at least one number, and one special character.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M06_R42</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1821,9 +1700,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1847,8 +1723,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1884,9 +1758,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1910,8 +1781,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1947,9 +1816,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>Constraint</t>
@@ -1963,9 +1829,6 @@
           <t>The application must be available for mobile devices with iOS and Android systems.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>Classification Change</t>
@@ -2006,9 +1869,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2032,8 +1892,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
